--- a/Downloads/Splitflask-Financials/handoff/CPA_TJ/SGM_2025_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/handoff/CPA_TJ/SGM_2025_Amendment_Packet.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,6 +93,16 @@
       <i val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="10">
@@ -213,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -325,6 +335,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -690,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -700,248 +713,447 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>⚠️ V2 CORRECTIONS APPLIED 2026-07-11 — SGM 2025 — 1120-S | FINAL AMENDED NET: ≈ +$85 (breakeven)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="40" t="inlineStr">
+        <is>
+          <t>These corrections supersede the figures in the body of this sheet. Use AMENDED NET from row below for filing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B3" s="41" t="inlineStr">
+        <is>
+          <t>Old Value</t>
+        </is>
+      </c>
+      <c r="C3" s="41" t="inlineStr">
+        <is>
+          <t>Corrected Value</t>
+        </is>
+      </c>
+      <c r="D3" s="41" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AMENDED NET INCOME (FINAL)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>−$11,915 (Assembly 3B)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>≈ +$85 (breakeven)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Augusta $16,500→$4,500 (+$12,000 removed from deductions). −$11,915 + $12,000 = +$85. SGM 2025 is a wind-down entity + Amazon nominee pass-through. Breakeven result is FAVORABLE vs filed −$32,900.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Augusta deduction — CORRECTED</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>$16,500 (as filed in packet)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>$4,500 (3 meetings × $1,500/day)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SPLT held 11 of 14 total Augusta days; SGM = remaining 3 days = $4,500. Minutes on file. $1,500/day = comp-supported (Giggster/Peerspace comps attached). 32001 Royceton Ct = personal residence; §280A(g) applies. Remove $12,000 from SGM 2025 deductions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>$148,164 SGM→SPLT — VOIDED</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Balance-sheet entry: $148,164</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VOIDED — REMOVE FROM BOTH ENTITIES</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PHANTOM: Amazon payouts went directly to SPLT's bank (SGM EIN, SPLT bank account). SGM never received the cash to transfer. Remove from SGM 2025 balance sheet entirely. No interco loan or capital treatment needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SBA EIDL liability — Schedule L</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Schedule L entry (TJ to complete)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>~$387,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Further paydown through 2025. Loan #7855987406; 3.75%/yr. Must appear on Schedule L. Check if 12 full $2,018/mo payments were made in 2025 — some may have come from another account; incremental interest ~$14,700 est. full-year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Entity characterization note</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Wind-down + nominee pass-through</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SGM 2025 real gross receipts ≈ $55,484 (Amazon $15,220.80 pre-switch + non-Amazon $34,252 + consulting $6,011). The $240,010 Amazon 1099-K is reported IN then $224,789.09 is nominated OUT to SPLT. SGM is NOT a $280K revenue entity in 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nominee 1099 — HARD INTERLOCK</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Required before filing</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MUST ISSUE before SGM 2025 or SPLT 2025 files</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SGM issues Form 1099 to SPLT for $224,789.09. Without it, SPLT reports income with no matching doc; IRS sees a mismatch. See Step 3 of V2 Action Plan for 8-step procedure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SBA EIDL interest 2025 — TJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>~$14,700 est. full-year</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CONFIRM captured</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pull SBA payment history. If $2,018 × 12 = $24,216 in payments in 2025, interest ~$14,700 at 3.75%. Confirm all interest is deducted, principal is NOT deducted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>--- END V2 CORRECTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>SGM / Social Gear Media LLC — 2025 Form 1120-S Amendment Packet</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>EIN 83-3077502  |  WF …8625  |  Tax Year 2025  |  CA S-Corp (1120-S)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>As-Filed</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Amended</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Gross Receipts (reported)</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B16" s="5" t="n">
         <v>130976</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C16" s="5" t="n">
         <v>55484</v>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Filed = pure bank deposits (owner loans $57,317 + interco $11,151 counted as revenue). Amended = real revenue only.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Amazon 1099-K (SGM TIN 83-3077502) — REPORTED IN</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="n">
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="9" t="n">
         <v>240009.89</v>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Full 1099-K reported IN on SGM 1120-S. Satisfies IRS CP2000 matching at $240K.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Amazon Nominee Distribution — DEDUCTED OUT</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="13" t="n">
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="13" t="n">
         <v>-224789.09</v>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Feb 5–Dec 31 Amazon orders earned by SPLT after account moved. Nominee 1099 issued SGM→SPLT EIN 33-3094308.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Amazon net on SGM (Jan 1–Feb 4 orders)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="n">
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="9" t="n">
         <v>15220.8</v>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>295 items / 302 units earned before cutoff. Source: Amazon order-date dashboard (Layer 7).</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Non-Amazon bank revenue</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="5" t="n">
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="5" t="n">
         <v>34252</v>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>SGM 2025 bank deposits — non-Amazon channels. Layer 7 classification, 720 rows, footed.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Consulting income (Teslarati + Video Elephant)</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="n">
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="9" t="n">
         <v>6011</v>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Named deposits in SGM 2025 bank. Layer 7. Confirmed NOT CB 2024 income.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Total Real Gross Receipts</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="18" t="n">
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="18" t="n">
         <v>55484</v>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>LOCKED = $15,220.80 + $34,252 + $6,011. Layer 7 + Layer 12.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Total Deductions</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="13" t="n">
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="13" t="n">
         <v>67398.78999999999</v>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>Itemized from SGM_2025_Txns — FINAL subject to TJ calls</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Net Ordinary Income / (Loss)</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B24" s="18" t="n">
         <v>-32900</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C24" s="18" t="n">
         <v>-11915</v>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>Favorable; does NOT raise tax — shallower than provisional −$19,027</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>KEY FINDINGS</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. DEPOSIT-BASIS ERROR — CORRECTED:  Filed return used total bank deposits ($130,976) as gross receipts. Deposits included $57,317 owner loans + $11,151 interco transfers = $68,468 of non-income, inflating filed gross by that amount. Additionally, a $7,024 reclassification (reversals/misc) was removed in Layer 12. Amendment restates on real-revenue basis: $55,484.</t>
         </is>
       </c>
-      <c r="B16" s="37" t="n"/>
-      <c r="C16" s="37" t="n"/>
-      <c r="D16" s="38" t="n"/>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="B27" s="37" t="n"/>
+      <c r="C27" s="37" t="n"/>
+      <c r="D27" s="38" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. AMAZON 1099-K NOMINEE MECHANICS (CENTERPIECE):  Amazon 1099-K $240,009.89 issued on SGM TIN because TIN update lagged when the account physically moved to SPLT (formed Jan 28, 2025). Resolution: SGM reports full $240,009.89 IN, deducts $224,789.09 OUT as Nominee Distribution, issues nominee 1099 to SPLT. SGM nets $15,220.80 (Jan 1–Feb 4 earned orders). TJ: also request corrected 1099-K from Amazon under SPLT TIN (belt-and-suspenders).</t>
         </is>
       </c>
-      <c r="B17" s="37" t="n"/>
-      <c r="C17" s="37" t="n"/>
-      <c r="D17" s="38" t="n"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="B28" s="37" t="n"/>
+      <c r="C28" s="37" t="n"/>
+      <c r="D28" s="38" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. FILED DEDUCTION DETAIL — TJ TO VERIFY (CB 2024 LESSON):  Filed gross $130,976 − filed net −$32,900 = implied filed expenses $163,876. Filed deduction schedule NOT available in source docs. TJ to provide filed 1120-S for deduction-by-deduction comparison. CB 2024 found $104K of unsubstantiated QuickBooks catch-all deductions — apply same scrutiny here.</t>
         </is>
       </c>
-      <c r="B18" s="37" t="n"/>
-      <c r="C18" s="37" t="n"/>
-      <c r="D18" s="38" t="n"/>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="B29" s="37" t="n"/>
+      <c r="C29" s="37" t="n"/>
+      <c r="D29" s="38" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. $148K SGM→SPLT TRANSFER — TJ LOAN-VS-CAPITAL DECISION:  $148,164 operating cash moved from SGM to SPLT as business shifted entities mid-2025. NOT P&amp;L. TJ: LOAN = interco receivable(SGM)/payable(SPLT); CAPITAL = permanent equity. $148K is material.</t>
         </is>
       </c>
-      <c r="B19" s="37" t="n"/>
-      <c r="C19" s="37" t="n"/>
-      <c r="D19" s="38" t="n"/>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="B30" s="37" t="n"/>
+      <c r="C30" s="37" t="n"/>
+      <c r="D30" s="38" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. AUGUSTA RENT $16,500 — PENDING TJ CONFIRMATION:  Bank-substantiated. Deductibility requires: (a) 14-day annual cap not exceeded, (b) no home-office double-stack. TJ confirms and approves inclusion.</t>
         </is>
       </c>
-      <c r="B20" s="37" t="n"/>
-      <c r="C20" s="37" t="n"/>
-      <c r="D20" s="38" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="B31" s="37" t="n"/>
+      <c r="C31" s="37" t="n"/>
+      <c r="D31" s="38" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Note: $34,600 provisional opex block replaced by $27,487.79 bank-itemized opex. Drop of $7,112 (block was over-stated). TJ adjustments (vehicle insurance $820, meals 50%, personal items ~$601, travel docs) could further reduce loss by $0–$1,421.</t>
         </is>
